--- a/Sources/DP_Codes_Completed.xlsx
+++ b/Sources/DP_Codes_Completed.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7aa1d8f405ba1d72/NDEDC_Production/Sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_CAC2225B572A2E508D4D3A1175AD8A4B382C416E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="0" yWindow="450" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2007,12 +2008,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2020,7 +2021,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2083,9 +2084,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2123,9 +2124,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2160,7 +2161,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2195,7 +2196,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2368,18 +2369,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E207"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2396,7 +2397,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2413,7 +2414,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2430,7 +2431,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2447,7 +2448,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2464,7 +2465,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2481,7 +2482,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2498,7 +2499,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -2515,7 +2516,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -2532,7 +2533,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -2549,7 +2550,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -2566,7 +2567,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -2583,7 +2584,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -2600,7 +2601,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -2617,7 +2618,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -2634,7 +2635,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -2651,7 +2652,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -2668,7 +2669,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -2685,7 +2686,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -2702,7 +2703,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -2719,7 +2720,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -2736,7 +2737,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -2753,7 +2754,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -2770,7 +2771,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -2787,7 +2788,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -2804,7 +2805,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -2821,7 +2822,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -2838,7 +2839,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -2855,7 +2856,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -2872,7 +2873,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -2889,7 +2890,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -2906,7 +2907,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>651</v>
       </c>
@@ -2923,7 +2924,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>651</v>
       </c>
@@ -2940,7 +2941,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>651</v>
       </c>
@@ -2957,7 +2958,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>651</v>
       </c>
@@ -2974,7 +2975,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>651</v>
       </c>
@@ -2991,7 +2992,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>651</v>
       </c>
@@ -3008,7 +3009,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>651</v>
       </c>
@@ -3025,7 +3026,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>651</v>
       </c>
@@ -3042,7 +3043,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>651</v>
       </c>
@@ -3059,7 +3060,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>651</v>
       </c>
@@ -3076,7 +3077,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>651</v>
       </c>
@@ -3093,7 +3094,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -3110,7 +3111,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -3127,7 +3128,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -3144,7 +3145,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -3161,7 +3162,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -3178,7 +3179,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>11</v>
       </c>
@@ -3195,7 +3196,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -3212,7 +3213,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -3229,7 +3230,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -3246,7 +3247,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -3263,7 +3264,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>11</v>
       </c>
@@ -3280,7 +3281,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>11</v>
       </c>
@@ -3297,7 +3298,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -3314,7 +3315,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -3331,7 +3332,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -3348,7 +3349,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -3365,7 +3366,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>12</v>
       </c>
@@ -3382,7 +3383,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -3399,7 +3400,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>12</v>
       </c>
@@ -3416,7 +3417,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>12</v>
       </c>
@@ -3433,7 +3434,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -3450,7 +3451,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>13</v>
       </c>
@@ -3467,7 +3468,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>13</v>
       </c>
@@ -3484,7 +3485,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>13</v>
       </c>
@@ -3501,7 +3502,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -3518,7 +3519,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>13</v>
       </c>
@@ -3535,7 +3536,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>14</v>
       </c>
@@ -3552,7 +3553,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>14</v>
       </c>
@@ -3569,7 +3570,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -3586,7 +3587,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -3603,7 +3604,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>14</v>
       </c>
@@ -3620,7 +3621,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>15</v>
       </c>
@@ -3637,7 +3638,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>15</v>
       </c>
@@ -3654,7 +3655,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>15</v>
       </c>
@@ -3671,7 +3672,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>15</v>
       </c>
@@ -3688,7 +3689,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>15</v>
       </c>
@@ -3705,7 +3706,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>15</v>
       </c>
@@ -3722,7 +3723,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>16</v>
       </c>
@@ -3739,7 +3740,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>16</v>
       </c>
@@ -3756,7 +3757,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>16</v>
       </c>
@@ -3773,7 +3774,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -3790,7 +3791,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -3807,7 +3808,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>16</v>
       </c>
@@ -3824,7 +3825,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>16</v>
       </c>
@@ -3841,7 +3842,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>16</v>
       </c>
@@ -3858,7 +3859,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>652</v>
       </c>
@@ -3875,7 +3876,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>652</v>
       </c>
@@ -3892,7 +3893,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>652</v>
       </c>
@@ -3909,7 +3910,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>652</v>
       </c>
@@ -3926,7 +3927,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>652</v>
       </c>
@@ -3943,7 +3944,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>653</v>
       </c>
@@ -3960,7 +3961,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>653</v>
       </c>
@@ -3977,7 +3978,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>653</v>
       </c>
@@ -3994,7 +3995,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>653</v>
       </c>
@@ -4011,7 +4012,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>653</v>
       </c>
@@ -4028,7 +4029,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>653</v>
       </c>
@@ -4045,7 +4046,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>17</v>
       </c>
@@ -4062,7 +4063,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -4079,7 +4080,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -4096,7 +4097,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -4113,7 +4114,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>19</v>
       </c>
@@ -4130,7 +4131,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>19</v>
       </c>
@@ -4147,7 +4148,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -4164,7 +4165,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>19</v>
       </c>
@@ -4181,7 +4182,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>20</v>
       </c>
@@ -4198,7 +4199,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>20</v>
       </c>
@@ -4215,7 +4216,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>20</v>
       </c>
@@ -4232,7 +4233,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>21</v>
       </c>
@@ -4249,7 +4250,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>21</v>
       </c>
@@ -4266,7 +4267,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>22</v>
       </c>
@@ -4283,7 +4284,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>23</v>
       </c>
@@ -4297,7 +4298,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>654</v>
       </c>
@@ -4314,7 +4315,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>654</v>
       </c>
@@ -4331,7 +4332,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>654</v>
       </c>
@@ -4348,7 +4349,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>654</v>
       </c>
@@ -4365,7 +4366,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>24</v>
       </c>
@@ -4382,7 +4383,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>24</v>
       </c>
@@ -4399,7 +4400,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>24</v>
       </c>
@@ -4416,7 +4417,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>24</v>
       </c>
@@ -4433,7 +4434,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>24</v>
       </c>
@@ -4450,7 +4451,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>24</v>
       </c>
@@ -4467,7 +4468,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>24</v>
       </c>
@@ -4484,7 +4485,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>24</v>
       </c>
@@ -4501,7 +4502,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>24</v>
       </c>
@@ -4518,7 +4519,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>24</v>
       </c>
@@ -4535,7 +4536,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>24</v>
       </c>
@@ -4552,7 +4553,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>24</v>
       </c>
@@ -4569,7 +4570,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>24</v>
       </c>
@@ -4586,7 +4587,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>655</v>
       </c>
@@ -4603,7 +4604,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>655</v>
       </c>
@@ -4620,7 +4621,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>655</v>
       </c>
@@ -4637,7 +4638,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>25</v>
       </c>
@@ -4654,7 +4655,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>25</v>
       </c>
@@ -4671,7 +4672,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>25</v>
       </c>
@@ -4688,7 +4689,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>25</v>
       </c>
@@ -4705,7 +4706,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>25</v>
       </c>
@@ -4722,7 +4723,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>25</v>
       </c>
@@ -4739,7 +4740,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>25</v>
       </c>
@@ -4756,7 +4757,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>25</v>
       </c>
@@ -4773,7 +4774,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>25</v>
       </c>
@@ -4790,7 +4791,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>25</v>
       </c>
@@ -4807,7 +4808,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -4824,7 +4825,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>26</v>
       </c>
@@ -4841,7 +4842,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>26</v>
       </c>
@@ -4858,7 +4859,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>26</v>
       </c>
@@ -4875,7 +4876,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>656</v>
       </c>
@@ -4892,7 +4893,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>656</v>
       </c>
@@ -4909,7 +4910,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>656</v>
       </c>
@@ -4926,7 +4927,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>656</v>
       </c>
@@ -4943,7 +4944,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>657</v>
       </c>
@@ -4960,7 +4961,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>27</v>
       </c>
@@ -4977,7 +4978,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>27</v>
       </c>
@@ -4994,7 +4995,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>27</v>
       </c>
@@ -5011,7 +5012,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>27</v>
       </c>
@@ -5028,7 +5029,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>27</v>
       </c>
@@ -5045,7 +5046,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>27</v>
       </c>
@@ -5062,7 +5063,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>28</v>
       </c>
@@ -5079,7 +5080,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>28</v>
       </c>
@@ -5096,7 +5097,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>29</v>
       </c>
@@ -5113,7 +5114,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>29</v>
       </c>
@@ -5130,7 +5131,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>30</v>
       </c>
@@ -5147,7 +5148,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>30</v>
       </c>
@@ -5164,7 +5165,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>31</v>
       </c>
@@ -5181,7 +5182,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>31</v>
       </c>
@@ -5198,7 +5199,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>31</v>
       </c>
@@ -5215,7 +5216,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>31</v>
       </c>
@@ -5232,7 +5233,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>31</v>
       </c>
@@ -5249,7 +5250,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>31</v>
       </c>
@@ -5266,7 +5267,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>31</v>
       </c>
@@ -5283,7 +5284,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>658</v>
       </c>
@@ -5300,7 +5301,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>658</v>
       </c>
@@ -5317,7 +5318,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>658</v>
       </c>
@@ -5334,7 +5335,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>658</v>
       </c>
@@ -5351,7 +5352,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>658</v>
       </c>
@@ -5368,7 +5369,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>32</v>
       </c>
@@ -5385,7 +5386,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>32</v>
       </c>
@@ -5402,7 +5403,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>32</v>
       </c>
@@ -5419,7 +5420,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>32</v>
       </c>
@@ -5436,7 +5437,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>32</v>
       </c>
@@ -5453,7 +5454,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>32</v>
       </c>
@@ -5470,7 +5471,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>33</v>
       </c>
@@ -5487,7 +5488,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>33</v>
       </c>
@@ -5504,7 +5505,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>33</v>
       </c>
@@ -5521,7 +5522,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>33</v>
       </c>
@@ -5538,7 +5539,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>33</v>
       </c>
@@ -5555,7 +5556,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>33</v>
       </c>
@@ -5572,7 +5573,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>33</v>
       </c>
@@ -5589,7 +5590,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>33</v>
       </c>
@@ -5606,7 +5607,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>33</v>
       </c>
@@ -5623,7 +5624,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>33</v>
       </c>
@@ -5640,7 +5641,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>33</v>
       </c>
@@ -5657,7 +5658,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>33</v>
       </c>
@@ -5674,7 +5675,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>33</v>
       </c>
@@ -5691,7 +5692,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>33</v>
       </c>
@@ -5708,7 +5709,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>34</v>
       </c>
@@ -5725,7 +5726,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>34</v>
       </c>
@@ -5742,7 +5743,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>34</v>
       </c>
@@ -5759,7 +5760,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>659</v>
       </c>
@@ -5776,7 +5777,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>659</v>
       </c>
@@ -5793,7 +5794,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>659</v>
       </c>
@@ -5810,7 +5811,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>659</v>
       </c>
@@ -5827,7 +5828,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>35</v>
       </c>
@@ -5844,7 +5845,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>35</v>
       </c>
@@ -5861,7 +5862,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>35</v>
       </c>
@@ -5878,7 +5879,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>35</v>
       </c>
@@ -5896,7 +5897,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E207"/>
+  <autoFilter ref="A1:E207" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
